--- a/Result/profitability/3430.xlsx
+++ b/Result/profitability/3430.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM50"/>
+  <dimension ref="A1:AM51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.51</v>
       </c>
       <c r="M2" t="n">
-        <v>0.76</v>
+        <v>0.8125</v>
       </c>
       <c r="N2" t="n">
-        <v>22.98125</v>
+        <v>22.71125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.96</v>
       </c>
       <c r="M3" t="n">
-        <v>0.53875</v>
+        <v>0.5449999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>20.60625</v>
+        <v>20.22625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.31</v>
       </c>
       <c r="M4" t="n">
-        <v>0.43</v>
+        <v>0.4375</v>
       </c>
       <c r="N4" t="n">
-        <v>18.88625</v>
+        <v>18.65125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>0.36</v>
       </c>
       <c r="M5" t="n">
-        <v>0.32875</v>
+        <v>0.4775</v>
       </c>
       <c r="N5" t="n">
-        <v>17.105</v>
+        <v>17.275</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.26</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4812500000000001</v>
+        <v>0.51875</v>
       </c>
       <c r="N6" t="n">
-        <v>16.02875</v>
+        <v>16.81125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.73</v>
       </c>
       <c r="M7" t="n">
-        <v>0.45625</v>
+        <v>0.48375</v>
       </c>
       <c r="N7" t="n">
-        <v>15.63875</v>
+        <v>15.915</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -6778,6 +6778,133 @@
       </c>
       <c r="AM50" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>3430</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>473</v>
+      </c>
+      <c r="D51" t="n">
+        <v>354</v>
+      </c>
+      <c r="E51" t="n">
+        <v>119</v>
+      </c>
+      <c r="F51" t="n">
+        <v>25.24</v>
+      </c>
+      <c r="G51" t="n">
+        <v>54</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>11.46%</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>4</v>
+      </c>
+      <c r="J51" t="n">
+        <v>58</v>
+      </c>
+      <c r="K51" t="n">
+        <v>42</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.9775</v>
+      </c>
+      <c r="N51" t="n">
+        <v>24.64625</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W51" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="X51" t="n">
+        <v>-0.1517241379310345</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0.08605851979345958</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.359999999999999</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.05695142378559459</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK51" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
